--- a/salon_forms/007_invisible_bead_extension_consultation_form--salon_forms.xlsx
+++ b/salon_forms/007_invisible_bead_extension_consultation_form--salon_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -949,7 +949,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>red_brown</t>
+          <t>red brown</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>chin_length</t>
+          <t>chin length</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ear_length</t>
+          <t>ear length</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>shoulder_length</t>
+          <t>shoulder length</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>waist_length</t>
+          <t>waist length</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>clip_in</t>
+          <t>clip in</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>tape_in</t>
+          <t>tape in</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>hand_tied</t>
+          <t>hand tied</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>micro_linked</t>
+          <t>micro linked</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>red_brown</t>
+          <t>red brown</t>
         </is>
       </c>
     </row>
